--- a/config/study_content_pack.xlsx
+++ b/config/study_content_pack.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="319">
   <si>
     <t>Action_Key</t>
   </si>
@@ -162,58 +162,34 @@
     <t>Normalized_Value</t>
   </si>
   <si>
-    <t>Cat 1 (Immediate)</t>
+    <t>Dead</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>SMART</t>
+  </si>
+  <si>
+    <t>Priority 1 (Red)</t>
   </si>
   <si>
     <t>Red</t>
   </si>
   <si>
-    <t>Cat 2 (Imminent)</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>Cat 3 (Urgent)</t>
+    <t>Priority 2 (Yellow)</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Priority 3 (Green)</t>
   </si>
   <si>
     <t>Green</t>
   </si>
   <si>
-    <t>Cat 4 (Semi-Urgent)</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>Cat 5 (Non-Urgent)</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Dead</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>SMART</t>
-  </si>
-  <si>
-    <t>Priority 1 (Red)</t>
-  </si>
-  <si>
-    <t>Priority 2 (Yellow)</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>Priority 3 (Green)</t>
-  </si>
-  <si>
-    <t>10S</t>
+    <t>TST</t>
   </si>
   <si>
     <t>P1 (Immediate)</t>
@@ -234,7 +210,7 @@
     <t>Scenario</t>
   </si>
   <si>
-    <t>Is_Tutorial</t>
+    <t>Is_Practice</t>
   </si>
   <si>
     <t>Visible_Text</t>
@@ -243,13 +219,10 @@
     <t>Avatar_File</t>
   </si>
   <si>
-    <t>Gold_Standard_SMART</t>
-  </si>
-  <si>
-    <t>Gold_Standard_10S</t>
-  </si>
-  <si>
-    <t>Gold_Standard_ATS</t>
+    <t>Ref_SMART</t>
+  </si>
+  <si>
+    <t>Ref_Standard_TST</t>
   </si>
   <si>
     <t>airway_obs_Text</t>
@@ -261,12 +234,6 @@
     <t>rr_Text</t>
   </si>
   <si>
-    <t>work_breath_Text</t>
-  </si>
-  <si>
-    <t>spo2_Text</t>
-  </si>
-  <si>
     <t>pulse_rad_Text</t>
   </si>
   <si>
@@ -276,33 +243,15 @@
     <t>cap_refill_Text</t>
   </si>
   <si>
-    <t>bp_Text</t>
-  </si>
-  <si>
     <t>hemorrhage_Text</t>
   </si>
   <si>
     <t>avpu_Text</t>
   </si>
   <si>
-    <t>gcs_Text</t>
-  </si>
-  <si>
-    <t>pupils_Text</t>
-  </si>
-  <si>
     <t>walk_Text</t>
   </si>
   <si>
-    <t>temp_Text</t>
-  </si>
-  <si>
-    <t>pain_Text</t>
-  </si>
-  <si>
-    <t>history_Text</t>
-  </si>
-  <si>
     <t>ent_01</t>
   </si>
   <si>
@@ -327,9 +276,6 @@
     <t>18/min</t>
   </si>
   <si>
-    <t>Unlabored breathing; no increased work of breathing.</t>
-  </si>
-  <si>
     <t>Present</t>
   </si>
   <si>
@@ -339,18 +285,9 @@
     <t>Alert</t>
   </si>
   <si>
-    <t>PERL</t>
-  </si>
-  <si>
     <t>Yes, I can walk.</t>
   </si>
   <si>
-    <t>Anxious.</t>
-  </si>
-  <si>
-    <t>Reports tripping while evacuating; no loss of consciousness; no meds or allergies.</t>
-  </si>
-  <si>
     <t>ent_02</t>
   </si>
   <si>
@@ -366,27 +303,15 @@
     <t>24/min</t>
   </si>
   <si>
-    <t>Mildly increased work of breathing; breathing slightly rapid.</t>
-  </si>
-  <si>
     <t>2s</t>
   </si>
   <si>
-    <t>100/60</t>
-  </si>
-  <si>
     <t>Concrete slab pinning lower body</t>
   </si>
   <si>
     <t>I can't move my legs.</t>
   </si>
   <si>
-    <t>Severe</t>
-  </si>
-  <si>
-    <t>Says a slab pinned both legs; severe pain; no known medical problems.</t>
-  </si>
-  <si>
     <t>ent_03</t>
   </si>
   <si>
@@ -408,33 +333,18 @@
     <t>Agonal, 6/min</t>
   </si>
   <si>
-    <t>Agonal respirations; minimal chest rise.</t>
-  </si>
-  <si>
     <t>Weak</t>
   </si>
   <si>
     <t>&gt;2s</t>
   </si>
   <si>
-    <t>80/40</t>
-  </si>
-  <si>
     <t>Trapped chest under a beam</t>
   </si>
   <si>
     <t>Unresponsive</t>
   </si>
   <si>
-    <t>Sluggish</t>
-  </si>
-  <si>
-    <t>35.0°C</t>
-  </si>
-  <si>
-    <t>Witness: found unresponsive after beam fell; unknown downtime.</t>
-  </si>
-  <si>
     <t>ent_04</t>
   </si>
   <si>
@@ -453,21 +363,9 @@
     <t>Jaw thrust attempted; no spontaneous respirations.</t>
   </si>
   <si>
-    <t>No spontaneous respirations.</t>
-  </si>
-  <si>
     <t>Completely buried under debris</t>
   </si>
   <si>
-    <t>Fixed/Dilated</t>
-  </si>
-  <si>
-    <t>Cold</t>
-  </si>
-  <si>
-    <t>No history available; buried for unknown duration.</t>
-  </si>
-  <si>
     <t>ent_05</t>
   </si>
   <si>
@@ -483,36 +381,21 @@
     <t>Rapid, 40/min</t>
   </si>
   <si>
-    <t>Severe respiratory distress; rapid, labored breathing.</t>
-  </si>
-  <si>
     <t>Thready</t>
   </si>
   <si>
     <t>&gt;3s</t>
   </si>
   <si>
-    <t>70/40</t>
-  </si>
-  <si>
     <t>Severe, spurting bleeding (Arterial)</t>
   </si>
   <si>
     <t>Unconscious</t>
   </si>
   <si>
-    <t>Dilated</t>
-  </si>
-  <si>
     <t>I can't move.</t>
   </si>
   <si>
-    <t>35.5°C</t>
-  </si>
-  <si>
-    <t>Says he was hit by falling debris; on daily aspirin; no allergies.</t>
-  </si>
-  <si>
     <t>ent_06</t>
   </si>
   <si>
@@ -528,21 +411,12 @@
     <t>Labored, 35/min</t>
   </si>
   <si>
-    <t>Labored breathing with accessory muscle use.</t>
-  </si>
-  <si>
-    <t>90/50</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
     <t>I can't walk, too painful.</t>
   </si>
   <si>
-    <t>Says leg was crushed; otherwise healthy; last meal this morning.</t>
-  </si>
-  <si>
     <t>ent_07</t>
   </si>
   <si>
@@ -558,15 +432,6 @@
     <t>&lt;2s</t>
   </si>
   <si>
-    <t>110/70</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Reports being trapped under shelving; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>ent_08</t>
   </si>
   <si>
@@ -585,9 +450,6 @@
     <t>I can't move my leg.</t>
   </si>
   <si>
-    <t>Says foot was pinned; denies head strike; no meds.</t>
-  </si>
-  <si>
     <t>ent_09</t>
   </si>
   <si>
@@ -603,18 +465,9 @@
     <t>22/min</t>
   </si>
   <si>
-    <t>Slightly rapid breathing; no obvious distress.</t>
-  </si>
-  <si>
     <t>No visible major injuries</t>
   </si>
   <si>
-    <t>Mild</t>
-  </si>
-  <si>
-    <t>Says she ran out; feels okay besides minor cuts; no PMH.</t>
-  </si>
-  <si>
     <t>ent_10</t>
   </si>
   <si>
@@ -630,12 +483,6 @@
     <t>28/min</t>
   </si>
   <si>
-    <t>Increased work of breathing; tachypneic.</t>
-  </si>
-  <si>
-    <t>States severe back pain after collapse; no meds; no allergies.</t>
-  </si>
-  <si>
     <t>ent_11</t>
   </si>
   <si>
@@ -651,9 +498,6 @@
     <t>Collapsed ceiling</t>
   </si>
   <si>
-    <t>No history available; unresponsive.</t>
-  </si>
-  <si>
     <t>ent_12</t>
   </si>
   <si>
@@ -669,21 +513,9 @@
     <t>Rapid, 35/min</t>
   </si>
   <si>
-    <t>Labored tachypnea; increased work of breathing.</t>
-  </si>
-  <si>
-    <t>85/50</t>
-  </si>
-  <si>
     <t>Severe pain and pelvic pressure (Internal/Crush)</t>
   </si>
   <si>
-    <t>35.8°C</t>
-  </si>
-  <si>
-    <t>Reports pelvic crush; severe pain; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>ent_13</t>
   </si>
   <si>
@@ -702,9 +534,6 @@
     <t>Minor lacerations</t>
   </si>
   <si>
-    <t>Says minor cuts only; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>ent_14</t>
   </si>
   <si>
@@ -717,12 +546,6 @@
     <t>ent_14.png</t>
   </si>
   <si>
-    <t>120/80</t>
-  </si>
-  <si>
-    <t>Says he cannot move legs; denies head injury; no meds.</t>
-  </si>
-  <si>
     <t>ent_15</t>
   </si>
   <si>
@@ -744,21 +567,6 @@
     <t>30/min</t>
   </si>
   <si>
-    <t>Labored breathing with increased effort.</t>
-  </si>
-  <si>
-    <t>90/60</t>
-  </si>
-  <si>
-    <t>36.0°C</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>Bystander: found face down, gurgling; unknown history.</t>
-  </si>
-  <si>
     <t>ent_16</t>
   </si>
   <si>
@@ -774,12 +582,6 @@
     <t>Labored, 28/min</t>
   </si>
   <si>
-    <t>Labored breathing; accessory muscle use.</t>
-  </si>
-  <si>
-    <t>Says chest feels tight after being pinned; no PMH.</t>
-  </si>
-  <si>
     <t>ent_17</t>
   </si>
   <si>
@@ -813,9 +615,6 @@
     <t>I can't move my hand.</t>
   </si>
   <si>
-    <t>Says hand was crushed; tetanus unknown; no meds.</t>
-  </si>
-  <si>
     <t>ent_19</t>
   </si>
   <si>
@@ -831,18 +630,9 @@
     <t>Rapid, shallow (38/min)</t>
   </si>
   <si>
-    <t>Rapid, shallow respirations; marked effort.</t>
-  </si>
-  <si>
-    <t>75/45</t>
-  </si>
-  <si>
     <t>Confused</t>
   </si>
   <si>
-    <t>Confused; repeats he was trapped; medical history unknown.</t>
-  </si>
-  <si>
     <t>ent_20</t>
   </si>
   <si>
@@ -873,15 +663,9 @@
     <t>vio_01.png</t>
   </si>
   <si>
-    <t>80/50</t>
-  </si>
-  <si>
     <t>Bubbling at wound site (Sucking Chest Wound)</t>
   </si>
   <si>
-    <t>Reports hearing gunshots; struck in chest; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>vio_02</t>
   </si>
   <si>
@@ -894,18 +678,12 @@
     <t>vio_02.png</t>
   </si>
   <si>
-    <t>Mildly increased work of breathing; tachypneic.</t>
-  </si>
-  <si>
     <t>Moderate venous bleeding</t>
   </si>
   <si>
     <t>I can walk, but it hurts.</t>
   </si>
   <si>
-    <t>Says she was grazed; takes no meds; no allergies.</t>
-  </si>
-  <si>
     <t>vio_03</t>
   </si>
   <si>
@@ -918,9 +696,6 @@
     <t>vio_03.png</t>
   </si>
   <si>
-    <t>No history available; multiple gunshot wounds reported by bystanders.</t>
-  </si>
-  <si>
     <t>vio_04</t>
   </si>
   <si>
@@ -936,9 +711,6 @@
     <t>Shrapnel wounds to the lower leg</t>
   </si>
   <si>
-    <t>Says shrapnel hit leg; ambulatory; no PMH.</t>
-  </si>
-  <si>
     <t>vio_05</t>
   </si>
   <si>
@@ -960,18 +732,9 @@
     <t>Rapid, shallow (45/min)</t>
   </si>
   <si>
-    <t>Severe respiratory distress; very rapid, shallow breathing.</t>
-  </si>
-  <si>
-    <t>60/40</t>
-  </si>
-  <si>
     <t>Massive blood loss from GSW to the neck (Arterial)</t>
   </si>
   <si>
-    <t>Bystander: shot in neck at close range; unknown history.</t>
-  </si>
-  <si>
     <t>vio_06</t>
   </si>
   <si>
@@ -987,12 +750,6 @@
     <t>25/min</t>
   </si>
   <si>
-    <t>Mild tachypnea; slight increased effort.</t>
-  </si>
-  <si>
-    <t>Says blast knocked her down; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>vio_07</t>
   </si>
   <si>
@@ -1011,9 +768,6 @@
     <t>I can walk, but I'm dizzy.</t>
   </si>
   <si>
-    <t>Says shrapnel hit back; feels dizzy; no meds.</t>
-  </si>
-  <si>
     <t>vio_08</t>
   </si>
   <si>
@@ -1026,15 +780,9 @@
     <t>vio_08.png</t>
   </si>
   <si>
-    <t>Severe respiratory distress; rapid breathing.</t>
-  </si>
-  <si>
     <t>GSW to the abdomen (Internal)</t>
   </si>
   <si>
-    <t>Bystander: shot in abdomen; became unresponsive; no history.</t>
-  </si>
-  <si>
     <t>vio_09</t>
   </si>
   <si>
@@ -1050,9 +798,6 @@
     <t>GSW to the arm, not bleeding heavily</t>
   </si>
   <si>
-    <t>Says arm was shot; last meal this morning; no meds.</t>
-  </si>
-  <si>
     <t>vio_10</t>
   </si>
   <si>
@@ -1068,15 +813,9 @@
     <t>Shallow, 35/min</t>
   </si>
   <si>
-    <t>Rapid, shallow respirations; increased effort.</t>
-  </si>
-  <si>
     <t>Moderate bleeding from GSW to the pelvis</t>
   </si>
   <si>
-    <t>Bystander: shot in pelvis; unresponsive; history unknown.</t>
-  </si>
-  <si>
     <t>vio_11</t>
   </si>
   <si>
@@ -1092,9 +831,6 @@
     <t>14/min</t>
   </si>
   <si>
-    <t>Says he is fine; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>vio_12</t>
   </si>
   <si>
@@ -1107,15 +843,9 @@
     <t>vio_12.png</t>
   </si>
   <si>
-    <t>Tachypneic; increased work of breathing.</t>
-  </si>
-  <si>
     <t>Multiple shrapnel wounds to the back and legs</t>
   </si>
   <si>
-    <t>Says multiple shrapnel hits; pain 7/10; no meds.</t>
-  </si>
-  <si>
     <t>vio_13</t>
   </si>
   <si>
@@ -1131,9 +861,6 @@
     <t>Massive bleeding from large shrapnel wound to the head</t>
   </si>
   <si>
-    <t>No history available; severe head injury.</t>
-  </si>
-  <si>
     <t>vio_14</t>
   </si>
   <si>
@@ -1146,18 +873,9 @@
     <t>vio_14.png</t>
   </si>
   <si>
-    <t>75/40</t>
-  </si>
-  <si>
     <t>Unknown (Unconscious)</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>Bystander: found gurgling, unresponsive; unknown history.</t>
-  </si>
-  <si>
     <t>vio_15</t>
   </si>
   <si>
@@ -1176,9 +894,6 @@
     <t>I can walk, if I had to.</t>
   </si>
   <si>
-    <t>Says arm was shot; no PMH; no meds.</t>
-  </si>
-  <si>
     <t>vio_16</t>
   </si>
   <si>
@@ -1197,9 +912,6 @@
     <t>I can't stand up.</t>
   </si>
   <si>
-    <t>Says knee was shot; cannot stand; no meds.</t>
-  </si>
-  <si>
     <t>vio_17</t>
   </si>
   <si>
@@ -1212,12 +924,6 @@
     <t>vio_17.png</t>
   </si>
   <si>
-    <t>Rapid, shallow breathing; increased effort.</t>
-  </si>
-  <si>
-    <t>Bystander: shot in abdomen; altered; no history.</t>
-  </si>
-  <si>
     <t>vio_18</t>
   </si>
   <si>
@@ -1233,15 +939,9 @@
     <t>Clear and without stridor. The wound looks to be from cheek to cheek</t>
   </si>
   <si>
-    <t>110/89</t>
-  </si>
-  <si>
     <t>GSW to the cheek with exit at other cheek. Mild bleeding. Controlled by pressure.</t>
   </si>
   <si>
-    <t>Says face was hit; mild bleeding; no PMH.</t>
-  </si>
-  <si>
     <t>vio_19</t>
   </si>
   <si>
@@ -1254,15 +954,9 @@
     <t>vio_19.png</t>
   </si>
   <si>
-    <t>Slightly rapid but unlabored.</t>
-  </si>
-  <si>
     <t>Minimal bleeding from GSW to the shoulder</t>
   </si>
   <si>
-    <t>Says shoulder was grazed; feels okay; no meds.</t>
-  </si>
-  <si>
     <t>vio_20</t>
   </si>
   <si>
@@ -1276,9 +970,6 @@
   </si>
   <si>
     <t>GSW to the head</t>
-  </si>
-  <si>
-    <t>No history available; head shot reported.</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1351,9 +1042,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1477,7 +1165,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C15" displayName="Tools" name="Tools" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C10" displayName="Tools" name="Tools" id="2">
   <tableColumns count="3">
     <tableColumn name="Tool_ID" id="1"/>
     <tableColumn name="Button_Label" id="2"/>
@@ -1488,34 +1176,25 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Z1000" displayName="Patients" name="Patients" id="3">
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Q1000" displayName="Patients" name="Patients" id="3">
+  <tableColumns count="17">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Patient_Name" id="2"/>
     <tableColumn name="Scenario" id="3"/>
-    <tableColumn name="Is_Tutorial" id="4"/>
+    <tableColumn name="Is_Practice" id="4"/>
     <tableColumn name="Visible_Text" id="5"/>
     <tableColumn name="Avatar_File" id="6"/>
-    <tableColumn name="Gold_Standard_SMART" id="7"/>
-    <tableColumn name="Gold_Standard_10S" id="8"/>
-    <tableColumn name="Gold_Standard_ATS" id="9"/>
-    <tableColumn name="airway_obs_Text" id="10"/>
-    <tableColumn name="airway_man_Text" id="11"/>
-    <tableColumn name="rr_Text" id="12"/>
-    <tableColumn name="work_breath_Text" id="13"/>
-    <tableColumn name="spo2_Text" id="14"/>
-    <tableColumn name="pulse_rad_Text" id="15"/>
-    <tableColumn name="pulse_rate_Text" id="16"/>
-    <tableColumn name="cap_refill_Text" id="17"/>
-    <tableColumn name="bp_Text" id="18"/>
-    <tableColumn name="hemorrhage_Text" id="19"/>
-    <tableColumn name="avpu_Text" id="20"/>
-    <tableColumn name="gcs_Text" id="21"/>
-    <tableColumn name="pupils_Text" id="22"/>
-    <tableColumn name="walk_Text" id="23"/>
-    <tableColumn name="temp_Text" id="24"/>
-    <tableColumn name="pain_Text" id="25"/>
-    <tableColumn name="history_Text" id="26"/>
+    <tableColumn name="Ref_SMART" id="7"/>
+    <tableColumn name="Ref_Standard_TST" id="8"/>
+    <tableColumn name="airway_obs_Text" id="9"/>
+    <tableColumn name="airway_man_Text" id="10"/>
+    <tableColumn name="rr_Text" id="11"/>
+    <tableColumn name="pulse_rad_Text" id="12"/>
+    <tableColumn name="pulse_rate_Text" id="13"/>
+    <tableColumn name="cap_refill_Text" id="14"/>
+    <tableColumn name="hemorrhage_Text" id="15"/>
+    <tableColumn name="avpu_Text" id="16"/>
+    <tableColumn name="walk_Text" id="17"/>
   </tableColumns>
   <tableStyleInfo name="Patients-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -2089,145 +1768,90 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="C9" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="7" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2250,3140 +1874,2128 @@
     <col customWidth="1" min="5" max="5" width="37.63"/>
     <col customWidth="1" min="6" max="6" width="13.75"/>
     <col customWidth="1" min="7" max="8" width="22.88"/>
-    <col customWidth="1" min="9" max="9" width="20.25"/>
-    <col customWidth="1" min="10" max="10" width="18.0"/>
-    <col customWidth="1" min="11" max="11" width="37.63"/>
-    <col customWidth="1" min="12" max="12" width="19.75"/>
-    <col customWidth="1" min="13" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="14" width="13.25"/>
-    <col customWidth="1" min="15" max="15" width="16.75"/>
-    <col customWidth="1" min="16" max="16" width="17.25"/>
-    <col customWidth="1" min="17" max="17" width="16.38"/>
-    <col customWidth="1" min="19" max="19" width="37.63"/>
-    <col customWidth="1" min="20" max="20" width="13.13"/>
-    <col customWidth="1" min="22" max="22" width="14.0"/>
-    <col customWidth="1" min="23" max="23" width="19.5"/>
-    <col customWidth="1" min="24" max="24" width="13.38"/>
-    <col customWidth="1" min="25" max="25" width="12.75"/>
-    <col customWidth="1" min="26" max="26" width="37.63"/>
+    <col customWidth="1" min="9" max="9" width="18.0"/>
+    <col customWidth="1" min="10" max="10" width="37.63"/>
+    <col customWidth="1" min="11" max="11" width="19.75"/>
+    <col customWidth="1" min="12" max="12" width="16.75"/>
+    <col customWidth="1" min="13" max="13" width="17.25"/>
+    <col customWidth="1" min="14" max="14" width="16.38"/>
+    <col customWidth="1" min="15" max="15" width="37.63"/>
+    <col customWidth="1" min="16" max="16" width="13.13"/>
+    <col customWidth="1" min="17" max="17" width="19.5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D2" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="M2" s="7">
+        <v>95.0</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" s="7">
-        <v>95.0</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U2" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y2" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z2" s="7" t="s">
-        <v>111</v>
+        <v>88</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D3" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="11">
-        <v>0.95</v>
+        <v>87</v>
+      </c>
+      <c r="M3" s="7">
+        <v>110.0</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P3" s="7">
-        <v>110.0</v>
+        <v>97</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U3" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D4" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="N4" s="11">
-        <v>0.8</v>
+        <v>106</v>
+      </c>
+      <c r="M4" s="7">
+        <v>135.0</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="P4" s="7">
-        <v>135.0</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U4" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>139</v>
+        <v>108</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D5" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U5" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X5" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D6" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0.85</v>
+        <v>122</v>
+      </c>
+      <c r="M6" s="7">
+        <v>150.0</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P6" s="7">
-        <v>150.0</v>
+        <v>124</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="U6" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="W6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="X6" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D7" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0.9</v>
+        <v>87</v>
+      </c>
+      <c r="M7" s="7">
+        <v>120.0</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P7" s="7">
-        <v>120.0</v>
+        <v>132</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U7" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D8" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.96</v>
+        <v>87</v>
+      </c>
+      <c r="M8" s="7">
+        <v>90.0</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="7">
-        <v>90.0</v>
+        <v>132</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S8" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U8" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y8" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z8" s="7" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D9" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0.97</v>
+        <v>87</v>
+      </c>
+      <c r="M9" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P9" s="7">
-        <v>100.0</v>
+        <v>132</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U9" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D10" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>196</v>
+        <v>87</v>
+      </c>
+      <c r="M10" s="7">
+        <v>105.0</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P10" s="7">
-        <v>105.0</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U10" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y10" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>199</v>
+        <v>150</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D11" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0.95</v>
+        <v>87</v>
+      </c>
+      <c r="M11" s="7">
+        <v>115.0</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P11" s="7">
-        <v>115.0</v>
+        <v>132</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U11" s="7">
-        <v>14.0</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W11" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y11" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z11" s="7" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D12" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="T12" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U12" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X12" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z12" s="7" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D13" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="N13" s="11">
-        <v>0.9</v>
+        <v>122</v>
+      </c>
+      <c r="M13" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P13" s="7">
-        <v>130.0</v>
+        <v>166</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U13" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y13" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z13" s="7" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D14" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="M14" s="7">
+        <v>88.0</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P14" s="7">
-        <v>88.0</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U14" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W14" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y14" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z14" s="7" t="s">
-        <v>229</v>
+        <v>172</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D15" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0.97</v>
+        <v>87</v>
+      </c>
+      <c r="M15" s="7">
+        <v>90.0</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P15" s="7">
-        <v>90.0</v>
+        <v>132</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U15" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y15" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>235</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D16" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0.88</v>
+        <v>106</v>
+      </c>
+      <c r="M16" s="7">
+        <v>125.0</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="P16" s="7">
-        <v>125.0</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="U16" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="V16" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="X16" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y16" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z16" s="7" t="s">
-        <v>247</v>
+      <c r="P16" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D17" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0.93</v>
+        <v>87</v>
+      </c>
+      <c r="M17" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P17" s="7">
-        <v>100.0</v>
+        <v>132</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U17" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y17" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z17" s="7" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D18" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="T18" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U18" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V18" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X18" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z18" s="7" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D19" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>262</v>
+        <v>196</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="11">
-        <v>0.98</v>
+        <v>87</v>
+      </c>
+      <c r="M19" s="7">
+        <v>98.0</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P19" s="7">
-        <v>98.0</v>
+        <v>198</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U19" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y19" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z19" s="7" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D20" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>269</v>
+        <v>202</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="N20" s="11">
-        <v>0.85</v>
+        <v>122</v>
+      </c>
+      <c r="M20" s="7">
+        <v>140.0</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P20" s="7">
-        <v>140.0</v>
+        <v>132</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="U20" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W20" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="X20" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z20" s="7" t="s">
-        <v>275</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D21" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>279</v>
+        <v>209</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U21" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X21" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z21" s="7" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D22" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>285</v>
+        <v>215</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="N22" s="11">
-        <v>0.85</v>
+        <v>106</v>
+      </c>
+      <c r="M22" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="P22" s="7">
-        <v>130.0</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U22" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="X22" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y22" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z22" s="7" t="s">
-        <v>288</v>
+        <v>216</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D23" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="N23" s="11">
-        <v>0.95</v>
+        <v>87</v>
+      </c>
+      <c r="M23" s="7">
+        <v>115.0</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P23" s="7">
-        <v>115.0</v>
+        <v>221</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="T23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U23" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y23" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z23" s="7" t="s">
-        <v>296</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D24" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U24" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V24" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X24" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y24" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z24" s="7" t="s">
-        <v>301</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>302</v>
+        <v>227</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D25" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>305</v>
+        <v>230</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="M25" s="7">
+        <v>95.0</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P25" s="7">
-        <v>95.0</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U25" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W25" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y25" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z25" s="7" t="s">
-        <v>307</v>
+        <v>231</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D26" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>311</v>
+        <v>235</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>312</v>
+        <v>237</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="N26" s="11">
-        <v>0.8</v>
+        <v>114</v>
+      </c>
+      <c r="M26" s="7">
+        <v>150.0</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="P26" s="7">
-        <v>150.0</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="T26" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="U26" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="V26" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="X26" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y26" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z26" s="7" t="s">
-        <v>318</v>
+        <v>239</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>319</v>
+        <v>240</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D27" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>321</v>
+        <v>242</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>324</v>
+        <v>87</v>
+      </c>
+      <c r="M27" s="7">
+        <v>110.0</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P27" s="7">
-        <v>110.0</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T27" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U27" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V27" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W27" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y27" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z27" s="7" t="s">
-        <v>325</v>
+        <v>132</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D28" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>328</v>
+        <v>247</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>329</v>
+        <v>248</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="N28" s="11">
-        <v>0.97</v>
+        <v>87</v>
+      </c>
+      <c r="M28" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P28" s="7">
-        <v>100.0</v>
+        <v>249</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R28" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S28" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="T28" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U28" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V28" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W28" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="Y28" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z28" s="7" t="s">
-        <v>332</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>333</v>
+        <v>251</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D29" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>335</v>
+        <v>253</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>336</v>
+        <v>254</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="N29" s="11">
-        <v>0.85</v>
+        <v>122</v>
+      </c>
+      <c r="M29" s="7">
+        <v>140.0</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P29" s="7">
-        <v>140.0</v>
+        <v>255</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R29" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="S29" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="T29" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U29" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="V29" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W29" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="X29" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y29" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z29" s="7" t="s">
-        <v>339</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>341</v>
+        <v>257</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D30" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>343</v>
+        <v>259</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N30" s="11">
-        <v>0.98</v>
+        <v>87</v>
+      </c>
+      <c r="M30" s="7">
+        <v>105.0</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P30" s="7">
-        <v>105.0</v>
+        <v>260</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R30" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S30" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="T30" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U30" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V30" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W30" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y30" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z30" s="7" t="s">
-        <v>345</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>346</v>
+        <v>261</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>347</v>
+        <v>262</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D31" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>102</v>
+        <v>265</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="N31" s="11">
-        <v>0.88</v>
+        <v>106</v>
+      </c>
+      <c r="M31" s="7">
+        <v>135.0</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="P31" s="7">
-        <v>135.0</v>
-      </c>
-      <c r="Q31" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R31" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="T31" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U31" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="V31" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="X31" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y31" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z31" s="7" t="s">
-        <v>353</v>
+        <v>266</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>354</v>
+        <v>267</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>355</v>
+        <v>268</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D32" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>356</v>
+        <v>269</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>357</v>
+        <v>270</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="M32" s="7">
+        <v>80.0</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P32" s="7">
-        <v>80.0</v>
-      </c>
-      <c r="S32" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="T32" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U32" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V32" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W32" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y32" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z32" s="7" t="s">
-        <v>359</v>
+        <v>132</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>360</v>
+        <v>272</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D33" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="N33" s="11">
-        <v>0.9</v>
+        <v>87</v>
+      </c>
+      <c r="M33" s="7">
+        <v>120.0</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P33" s="7">
-        <v>120.0</v>
+        <v>276</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="R33" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="T33" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U33" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V33" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W33" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y33" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z33" s="7" t="s">
-        <v>366</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>367</v>
+        <v>277</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>368</v>
+        <v>278</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D34" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>369</v>
+        <v>279</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>370</v>
+        <v>280</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>144</v>
+        <v>281</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q34" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R34" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S34" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="T34" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U34" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V34" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X34" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y34" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z34" s="7" t="s">
-        <v>372</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>373</v>
+        <v>282</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>374</v>
+        <v>283</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D35" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>375</v>
+        <v>284</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>376</v>
+        <v>285</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="N35" s="11">
-        <v>0.8</v>
+        <v>122</v>
+      </c>
+      <c r="M35" s="7">
+        <v>140.0</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P35" s="7">
-        <v>140.0</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="T35" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U35" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="V35" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="X35" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y35" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z35" s="7" t="s">
-        <v>380</v>
+        <v>286</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>382</v>
+        <v>288</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D36" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>383</v>
+        <v>289</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>384</v>
+        <v>290</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N36" s="11">
-        <v>0.97</v>
+        <v>87</v>
+      </c>
+      <c r="M36" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P36" s="7">
-        <v>100.0</v>
+        <v>291</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R36" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S36" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="T36" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U36" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V36" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W36" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="Y36" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z36" s="7" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>389</v>
+        <v>294</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D37" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>390</v>
+        <v>295</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="11">
-        <v>0.98</v>
+        <v>87</v>
+      </c>
+      <c r="M37" s="7">
+        <v>92.0</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P37" s="7">
-        <v>92.0</v>
+        <v>297</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R37" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="T37" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U37" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V37" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W37" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="Y37" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z37" s="7" t="s">
-        <v>394</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>395</v>
+        <v>299</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>396</v>
+        <v>300</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D38" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>397</v>
+        <v>301</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>398</v>
+        <v>302</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>102</v>
+        <v>265</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="N38" s="11">
-        <v>0.88</v>
+        <v>106</v>
+      </c>
+      <c r="M38" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="P38" s="7">
-        <v>130.0</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="R38" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="S38" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="T38" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U38" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="V38" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="X38" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y38" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z38" s="7" t="s">
-        <v>400</v>
+        <v>255</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>401</v>
+        <v>303</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D39" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>403</v>
+        <v>305</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>404</v>
+        <v>306</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>64</v>
+        <v>307</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>405</v>
+        <v>85</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="N39" s="11">
-        <v>0.98</v>
+        <v>87</v>
+      </c>
+      <c r="M39" s="7">
+        <v>110.0</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P39" s="7">
-        <v>110.0</v>
+        <v>308</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R39" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="T39" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U39" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V39" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y39" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z39" s="7" t="s">
-        <v>408</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>409</v>
+        <v>309</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D40" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>412</v>
+        <v>312</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="M40" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="N40" s="11">
-        <v>0.97</v>
+        <v>87</v>
+      </c>
+      <c r="M40" s="7">
+        <v>105.0</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P40" s="7">
-        <v>105.0</v>
+        <v>313</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="T40" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U40" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="V40" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="W40" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y40" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z40" s="7" t="s">
-        <v>415</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>416</v>
+        <v>314</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>283</v>
+        <v>213</v>
       </c>
       <c r="D41" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>418</v>
+        <v>316</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>419</v>
+        <v>317</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>144</v>
+        <v>318</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="S41" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="T41" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="U41" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="V41" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="X41" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z41" s="7" t="s">
-        <v>421</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1"/>
